--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,9 +520,68 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2025-10-14T18:08:00.835Z</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ELOIT</v>
+      </c>
+      <c r="D3" t="str">
+        <v>partner@photall.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v>0651334512</v>
+      </c>
+      <c r="F3" t="str">
+        <v>https://photall.com</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2 rue de la Peyrolerie</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Capdenac</v>
+      </c>
+      <c r="I3" t="str">
+        <v>46100</v>
+      </c>
+      <c r="J3" t="str">
+        <v>FR</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Photo, Video, Film</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>No</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,68 +461,9 @@
         <v>Consent</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2025-10-14T18:21:27.715Z</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ELOIT</v>
-      </c>
-      <c r="D2" t="str">
-        <v>contact@eloit.com</v>
-      </c>
-      <c r="E2" t="str">
-        <v>0651334512</v>
-      </c>
-      <c r="F2" t="str">
-        <v>https://eloit.com</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2 rue de la Peyrolerie</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Capdenac</v>
-      </c>
-      <c r="I2" t="str">
-        <v>46100</v>
-      </c>
-      <c r="J2" t="str">
-        <v>FR</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Photo, Video, Film</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>No</v>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -458,68 +458,9 @@
         <v>Consent</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2025-10-15T05:39:50.370Z</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Eloit</v>
-      </c>
-      <c r="C2" t="str">
-        <v>e@e.com</v>
-      </c>
-      <c r="D2" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v>France</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Prints</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:T2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -458,9 +458,71 @@
         <v>Consent</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2025-10-15T07:28:10.021Z</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ccccc</v>
+      </c>
+      <c r="C2" t="str">
+        <v>cc@dd.com</v>
+      </c>
+      <c r="D2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="E2" t="str">
+        <v>0606</v>
+      </c>
+      <c r="F2" t="str">
+        <v>photall.com</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>France</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Prints</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,9 +520,71 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2025-10-15T07:42:02.913Z</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Ngoc boite</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ngoc@outlook.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="E3" t="str">
+        <v>12346856263</v>
+      </c>
+      <c r="F3" t="str">
+        <v>ngoc.com</v>
+      </c>
+      <c r="G3" t="str">
+        <v>123 rue abc</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Batiment BCB</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Capdenac</v>
+      </c>
+      <c r="J3" t="str">
+        <v>12345</v>
+      </c>
+      <c r="K3" t="str">
+        <v>France</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Polaroid/Instax, Negatives 35mm</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>8mm, Super 8</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v>Digital8, U-Matic, MiniDV</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>USB, DVD/Blu-ray</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -550,19 +550,19 @@
         <v>Yes</v>
       </c>
       <c r="V2" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
       </c>
       <c r="W2" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="X2" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="Y2" t="str">
-        <v/>
+        <v>45.5186</v>
       </c>
       <c r="Z2" t="str">
-        <v/>
+        <v>1.9981</v>
       </c>
       <c r="AA2" t="str">
         <v>eloit-inc</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -559,10 +559,10 @@
         <v>TRUE</v>
       </c>
       <c r="Y2" t="str">
-        <v>45.5186</v>
+        <v>44.581099038048706</v>
       </c>
       <c r="Z2" t="str">
-        <v>1.9981</v>
+        <v>2.070213083026406</v>
       </c>
       <c r="AA2" t="str">
         <v>eloit-inc</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -568,9 +568,175 @@
         <v>eloit-inc</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2025-10-15T15:08:24.643Z</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Lebolabo</v>
+      </c>
+      <c r="C3" t="str">
+        <v>test@lebolabo.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="E3" t="str">
+        <v>+33 6 51 33 12</v>
+      </c>
+      <c r="F3" t="str">
+        <v>https://lebolabo.com/</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2 rue de la Soif</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Bordeaux</v>
+      </c>
+      <c r="J3" t="str">
+        <v>46130</v>
+      </c>
+      <c r="K3" t="str">
+        <v>France</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Prints, Albums</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>USB</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>Lebolabo réalise des numérisations photo par lot en basse résolution afin que vous puissiez visualiser vos images facilement sur un appareil numérique tel qu’un écran d’ordinateur, une tablette ou un smartphone (IPhone ou Android) et à moindre coût.</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="W3" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="X3" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>lebolabo</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2025-10-15T15:14:23.310Z</v>
+      </c>
+      <c r="B4" t="str">
+        <v>NGOC TEST</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ngoc@test.com</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="E4" t="str">
+        <v>12 65 25 15 45</v>
+      </c>
+      <c r="F4" t="str">
+        <v>test.com</v>
+      </c>
+      <c r="G4" t="str">
+        <v>68 Av. Jean Jaurès</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Souillac</v>
+      </c>
+      <c r="J4" t="str">
+        <v>46200</v>
+      </c>
+      <c r="K4" t="str">
+        <v>France</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Prints, Negatives 35mm</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>8mm, Super 8</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v>VHS, MiniDV, Digital8</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>USB, DVD/Blu-ray</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>description test</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="V4" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="W4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>44.9046780724082</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>1.4671430115554622</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>ngoc-test</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,88 +397,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AC4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Timestamp</v>
       </c>
       <c r="B1" t="str">
+        <v>Partner Type</v>
+      </c>
+      <c r="C1" t="str">
         <v>Partner Name</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Email</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Email_Public</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Phone</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>Phone_Public</v>
+      </c>
+      <c r="H1" t="str">
         <v>Website</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Address</v>
       </c>
-      <c r="H1" t="str">
-        <v>Complément d'adresse</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
+        <v>Address Line 2</v>
+      </c>
+      <c r="K1" t="str">
         <v>City</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>Postal Code</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>Country</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>Photo Formats</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>Other Photo</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>Film Formats</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>Other Film</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>Video Cassettes</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>Other Video</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>Delivery</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>Other Delivery</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>Public Description</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>Consent</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>Status</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>Is_Active</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>Show_On_Map</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>lat</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>lng</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>slug</v>
       </c>
     </row>
@@ -487,84 +493,90 @@
         <v>2025-10-15T10:16:29.295Z</v>
       </c>
       <c r="B2" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C2" t="str">
         <v>Eloit Inc</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>stephane@eloit.com</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>+33 6 51 33 45 12</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="H2" t="str">
         <v>photall.com</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>2 rue de la Peyrolerie</v>
       </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
         <v>Capdenac</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>46130</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>France</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>Prints, Negatives 35mm, Slides 35mm, Medium format 120/220</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>Super 8, 8mm</v>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v>Betamax, VHS, Digital8</v>
       </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
         <v>USB, External drive</v>
       </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str" xml:space="preserve">
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str" xml:space="preserve">
         <v xml:space="preserve">La solution idéale pour sauvegarder vos souvenirs et les visionner facilement !
 Utilisation de scanners professionnels.
 Correction colorimétrique des diapositives scannées afin d’améliorer le rendu des couleurs et minimiser les – dégâts du temps.
 Optimisation des contrastes et de l’exposition afin d’adapter les images à une consultation sur un écran d’ordinateur ou de TV (le contraste et l’exposition sont initialement prévus pour une projection sur écran avec une ampoule à forte intensité).</v>
       </c>
-      <c r="U2" t="str">
+      <c r="W2" t="str">
         <v>Yes</v>
       </c>
-      <c r="V2" t="str">
+      <c r="X2" t="str">
         <v>Approved</v>
       </c>
-      <c r="W2" t="str">
+      <c r="Y2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="X2" t="str">
+      <c r="Z2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="Y2" t="str">
+      <c r="AA2" t="str">
         <v>44.581099038048706</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AB2" t="str">
         <v>2.070213083026406</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AC2" t="str">
         <v>eloit-inc</v>
       </c>
     </row>
@@ -573,44 +585,44 @@
         <v>2025-10-15T15:08:24.643Z</v>
       </c>
       <c r="B3" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C3" t="str">
         <v>Lebolabo</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>test@lebolabo.com</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>+33 6 51 33 12</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="H3" t="str">
         <v>https://lebolabo.com/</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>2 rue de la Soif</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>Bordeaux</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>46130</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>France</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
         <v>Prints, Albums</v>
       </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
       <c r="O3" t="str">
         <v/>
       </c>
@@ -621,33 +633,39 @@
         <v/>
       </c>
       <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
         <v>USB</v>
       </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
         <v>Lebolabo réalise des numérisations photo par lot en basse résolution afin que vous puissiez visualiser vos images facilement sur un appareil numérique tel qu’un écran d’ordinateur, une tablette ou un smartphone (IPhone ou Android) et à moindre coût.</v>
       </c>
-      <c r="U3" t="str">
+      <c r="W3" t="str">
         <v>Yes</v>
       </c>
-      <c r="V3" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="W3" t="str">
+      <c r="X3" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y3" t="str">
         <v>FALSE</v>
       </c>
-      <c r="X3" t="str">
+      <c r="Z3" t="str">
         <v>FALSE</v>
       </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
-      <c r="Z3" t="str">
-        <v/>
-      </c>
       <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
         <v>lebolabo</v>
       </c>
     </row>
@@ -656,87 +674,93 @@
         <v>2025-10-15T15:14:23.310Z</v>
       </c>
       <c r="B4" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C4" t="str">
         <v>NGOC TEST</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>ngoc@test.com</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>12 65 25 15 45</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="H4" t="str">
         <v>test.com</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>68 Av. Jean Jaurès</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>Souillac</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>46200</v>
       </c>
-      <c r="K4" t="str">
+      <c r="M4" t="str">
         <v>France</v>
       </c>
-      <c r="L4" t="str">
+      <c r="N4" t="str">
         <v>Prints, Negatives 35mm</v>
       </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>8mm, Super 8</v>
       </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
         <v>VHS, MiniDV, Digital8</v>
       </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
         <v>USB, DVD/Blu-ray</v>
       </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
         <v>description test</v>
       </c>
-      <c r="U4" t="str">
+      <c r="W4" t="str">
         <v>Yes</v>
       </c>
-      <c r="V4" t="str">
+      <c r="X4" t="str">
         <v>Approved</v>
       </c>
-      <c r="W4" t="str">
+      <c r="Y4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="X4" t="str">
+      <c r="Z4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="Y4" t="str">
+      <c r="AA4" t="str">
         <v>44.9046780724082</v>
       </c>
-      <c r="Z4" t="str">
+      <c r="AB4" t="str">
         <v>1.4671430115554622</v>
       </c>
-      <c r="AA4" t="str">
+      <c r="AC4" t="str">
         <v>ngoc-test</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -562,7 +562,7 @@
         <v>Yes</v>
       </c>
       <c r="X2" t="str">
-        <v>Approved</v>
+        <v>Pending</v>
       </c>
       <c r="Y2" t="str">
         <v>TRUE</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -488,39 +488,39 @@
         <v>slug</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>2025-10-15T10:16:29.295Z</v>
+        <v>2025-10-15T15:08:24.643Z</v>
       </c>
       <c r="B2" t="str">
         <v>digitization</v>
       </c>
       <c r="C2" t="str">
-        <v>Eloit Inc</v>
+        <v>Lebolabo</v>
       </c>
       <c r="D2" t="str">
-        <v>stephane@eloit.com</v>
+        <v>test@lebolabo.com</v>
       </c>
       <c r="E2" t="str">
         <v>TRUE</v>
       </c>
       <c r="F2" t="str">
-        <v>+33 6 51 33 45 12</v>
+        <v>+33 6 51 33 12</v>
       </c>
       <c r="G2" t="str">
         <v>FALSE</v>
       </c>
       <c r="H2" t="str">
-        <v>photall.com</v>
+        <v>https://lebolabo.com/</v>
       </c>
       <c r="I2" t="str">
-        <v>2 rue de la Peyrolerie</v>
+        <v>2 rue de la Soif</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>Capdenac</v>
+        <v>Bordeaux</v>
       </c>
       <c r="L2" t="str">
         <v>46130</v>
@@ -529,123 +529,120 @@
         <v>France</v>
       </c>
       <c r="N2" t="str">
-        <v>Prints, Negatives 35mm, Slides 35mm, Medium format 120/220</v>
+        <v>Prints, Albums</v>
       </c>
       <c r="O2" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>Super 8, 8mm</v>
+        <v/>
       </c>
       <c r="Q2" t="str">
         <v/>
       </c>
       <c r="R2" t="str">
-        <v>Betamax, VHS, Digital8</v>
+        <v/>
       </c>
       <c r="S2" t="str">
         <v/>
       </c>
       <c r="T2" t="str">
-        <v>USB, External drive</v>
+        <v>USB</v>
       </c>
       <c r="U2" t="str">
         <v/>
       </c>
-      <c r="V2" t="str" xml:space="preserve">
-        <v xml:space="preserve">La solution idéale pour sauvegarder vos souvenirs et les visionner facilement !
-Utilisation de scanners professionnels.
-Correction colorimétrique des diapositives scannées afin d’améliorer le rendu des couleurs et minimiser les – dégâts du temps.
-Optimisation des contrastes et de l’exposition afin d’adapter les images à une consultation sur un écran d’ordinateur ou de TV (le contraste et l’exposition sont initialement prévus pour une projection sur écran avec une ampoule à forte intensité).</v>
+      <c r="V2" t="str">
+        <v>Lebolabo réalise des numérisations photo par lot en basse résolution afin que vous puissiez visualiser vos images facilement sur un appareil numérique tel qu’un écran d’ordinateur, une tablette ou un smartphone (IPhone ou Android) et à moindre coût.</v>
       </c>
       <c r="W2" t="str">
         <v>Yes</v>
       </c>
       <c r="X2" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
       </c>
       <c r="Y2" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="Z2" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AA2" t="str">
-        <v>44.581099038048706</v>
+        <v/>
       </c>
       <c r="AB2" t="str">
-        <v>2.070213083026406</v>
+        <v/>
       </c>
       <c r="AC2" t="str">
-        <v>eloit-inc</v>
+        <v>lebolabo</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-10-15T15:08:24.643Z</v>
+        <v>2025-10-15T15:14:23.310Z</v>
       </c>
       <c r="B3" t="str">
         <v>digitization</v>
       </c>
       <c r="C3" t="str">
-        <v>Lebolabo</v>
+        <v>NGOC TEST</v>
       </c>
       <c r="D3" t="str">
-        <v>test@lebolabo.com</v>
+        <v>ngoc@test.com</v>
       </c>
       <c r="E3" t="str">
         <v>TRUE</v>
       </c>
       <c r="F3" t="str">
-        <v>+33 6 51 33 12</v>
+        <v>12 65 25 15 45</v>
       </c>
       <c r="G3" t="str">
         <v>FALSE</v>
       </c>
       <c r="H3" t="str">
-        <v>https://lebolabo.com/</v>
+        <v>test.com</v>
       </c>
       <c r="I3" t="str">
-        <v>2 rue de la Soif</v>
+        <v>68 Av. Jean Jaurès</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Bordeaux</v>
+        <v>Souillac</v>
       </c>
       <c r="L3" t="str">
-        <v>46130</v>
+        <v>46200</v>
       </c>
       <c r="M3" t="str">
         <v>France</v>
       </c>
       <c r="N3" t="str">
-        <v>Prints, Albums</v>
+        <v>Prints, Negatives 35mm</v>
       </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>8mm, Super 8</v>
       </c>
       <c r="Q3" t="str">
         <v/>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>VHS, MiniDV, Digital8</v>
       </c>
       <c r="S3" t="str">
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>USB</v>
+        <v>USB, DVD/Blu-ray</v>
       </c>
       <c r="U3" t="str">
         <v/>
       </c>
       <c r="V3" t="str">
-        <v>Lebolabo réalise des numérisations photo par lot en basse résolution afin que vous puissiez visualiser vos images facilement sur un appareil numérique tel qu’un écran d’ordinateur, une tablette ou un smartphone (IPhone ou Android) et à moindre coût.</v>
+        <v>description test</v>
       </c>
       <c r="W3" t="str">
         <v>Yes</v>
@@ -654,113 +651,24 @@
         <v>Approved</v>
       </c>
       <c r="Y3" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="Z3" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AA3" t="str">
-        <v/>
+        <v>44.9046780724082</v>
       </c>
       <c r="AB3" t="str">
-        <v/>
+        <v>1.4671430115554622</v>
       </c>
       <c r="AC3" t="str">
-        <v>lebolabo</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2025-10-15T15:14:23.310Z</v>
-      </c>
-      <c r="B4" t="str">
-        <v>digitization</v>
-      </c>
-      <c r="C4" t="str">
-        <v>NGOC TEST</v>
-      </c>
-      <c r="D4" t="str">
-        <v>ngoc@test.com</v>
-      </c>
-      <c r="E4" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="F4" t="str">
-        <v>12 65 25 15 45</v>
-      </c>
-      <c r="G4" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="H4" t="str">
-        <v>test.com</v>
-      </c>
-      <c r="I4" t="str">
-        <v>68 Av. Jean Jaurès</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v>Souillac</v>
-      </c>
-      <c r="L4" t="str">
-        <v>46200</v>
-      </c>
-      <c r="M4" t="str">
-        <v>France</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Prints, Negatives 35mm</v>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>8mm, Super 8</v>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v>VHS, MiniDV, Digital8</v>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v>USB, DVD/Blu-ray</v>
-      </c>
-      <c r="U4" t="str">
-        <v/>
-      </c>
-      <c r="V4" t="str">
-        <v>description test</v>
-      </c>
-      <c r="W4" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="X4" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="Y4" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="Z4" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AA4" t="str">
-        <v>44.9046780724082</v>
-      </c>
-      <c r="AB4" t="str">
-        <v>1.4671430115554622</v>
-      </c>
-      <c r="AC4" t="str">
         <v>ngoc-test</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -666,9 +666,98 @@
         <v>ngoc-test</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2025-10-15T17:06:52.030Z</v>
+      </c>
+      <c r="B4" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C4" t="str">
+        <v>eeeee</v>
+      </c>
+      <c r="D4" t="str">
+        <v>sss2ooe@ddd.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="H4" t="str">
+        <v>ddd.com</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>Prints</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>Digital8</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>External drive, USB</v>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v>ddd.comddd.comddd.comddd.comddd.com</v>
+      </c>
+      <c r="W4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AA4">
+        <v>44.44543449469977</v>
+      </c>
+      <c r="AB4">
+        <v>1.4452141176732154</v>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -567,11 +567,11 @@
       <c r="Z2" t="str">
         <v>FALSE</v>
       </c>
-      <c r="AA2" t="str">
-        <v/>
-      </c>
-      <c r="AB2" t="str">
-        <v/>
+      <c r="AA2">
+        <v>30.4</v>
+      </c>
+      <c r="AB2">
+        <v>1.5</v>
       </c>
       <c r="AC2" t="str">
         <v>lebolabo</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -514,7 +514,7 @@
         <v>https://lebolabo.com/</v>
       </c>
       <c r="I2" t="str">
-        <v>2 rue de la Soif</v>
+        <v>48 Rue Bergeret</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -523,7 +523,7 @@
         <v>Bordeaux</v>
       </c>
       <c r="L2" t="str">
-        <v>46130</v>
+        <v>33000</v>
       </c>
       <c r="M2" t="str">
         <v>France</v>
@@ -568,10 +568,10 @@
         <v>FALSE</v>
       </c>
       <c r="AA2">
-        <v>30.4</v>
+        <v>44.831897557776564</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>-0.5678587426661484</v>
       </c>
       <c r="AC2" t="str">
         <v>lebolabo</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -508,7 +508,7 @@
         <v>+33 6 51 33 12</v>
       </c>
       <c r="G2" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="H2" t="str">
         <v>https://lebolabo.com/</v>
@@ -562,10 +562,10 @@
         <v>Approved</v>
       </c>
       <c r="Y2" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="Z2" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AA2">
         <v>44.831897557776564</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -488,7 +488,7 @@
         <v>slug</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>2025-10-15T15:08:24.643Z</v>
       </c>
@@ -552,8 +552,9 @@
       <c r="U2" t="str">
         <v/>
       </c>
-      <c r="V2" t="str">
-        <v>Lebolabo réalise des numérisations photo par lot en basse résolution afin que vous puissiez visualiser vos images facilement sur un appareil numérique tel qu’un écran d’ordinateur, une tablette ou un smartphone (IPhone ou Android) et à moindre coût.</v>
+      <c r="V2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lebolabo réalise des numérisations photo par lot en basse résolution afin que vous puissiez visualiser vos images facilement sur un appareil numérique tel qu’un écran d’ordinateur, une tablette ou un smartphone (IPhone ou Android) et à moindre coût.
+Lebolabo réalise des numérisations photo par lot en basse résolution afin que vous puissiez visualiser vos images facilement sur un appareil numérique tel qu’un écran d’ordinateur, une tablette ou un smartphone (IPhone ou Android) et à moindre coût.</v>
       </c>
       <c r="W2" t="str">
         <v>Yes</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -756,9 +756,899 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2025-10-16T08:13:22.805Z</v>
+      </c>
+      <c r="B5" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Swiss Memory Lab</v>
+      </c>
+      <c r="D5" t="str">
+        <v>contact@swissmemorylab.ch</v>
+      </c>
+      <c r="E5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F5" t="str">
+        <v>+41 22 345 6789</v>
+      </c>
+      <c r="G5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H5" t="str">
+        <v>swissmemorylab.ch</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Rue du Rhône 45</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>Geneva</v>
+      </c>
+      <c r="L5" t="str">
+        <v>1204</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Switzerland</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Prints, Negatives 35mm, Slides 35mm</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v>Super 8, 16mm</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>VHS, MiniDV</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v>In-person, Mail</v>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v>Spécialiste de la numérisation de médias depuis 1995. Nous offrons des services professionnels de haute qualité pour préserver vos souvenirs les plus précieux.</v>
+      </c>
+      <c r="W5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>46.2044</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>6.1432</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>swiss-memory-lab</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2025-10-16T08:13:24.713Z</v>
+      </c>
+      <c r="B6" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Zurich Digital Archives</v>
+      </c>
+      <c r="D6" t="str">
+        <v>info@zurichdigital.ch</v>
+      </c>
+      <c r="E6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F6" t="str">
+        <v>+41 44 123 4567</v>
+      </c>
+      <c r="G6" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="H6" t="str">
+        <v>zurichdigital.ch</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Bahnhofstrasse 100</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>Zurich</v>
+      </c>
+      <c r="L6" t="str">
+        <v>8001</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Switzerland</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Prints, Albums, Negatives 35mm</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v>8mm, Super 8</v>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>VHS, Betamax, MiniDV</v>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v>In-person, Digital download</v>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v>Service de numérisation professionnel au cœur de Zurich. Technologie de pointe pour des résultats exceptionnels.</v>
+      </c>
+      <c r="W6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X6" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>47.3769</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>8.5417</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>zurich-digital-archives</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2025-10-16T08:13:26.457Z</v>
+      </c>
+      <c r="B7" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Lausanne Photo Scan</v>
+      </c>
+      <c r="D7" t="str">
+        <v>contact@lausannephotoscan.ch</v>
+      </c>
+      <c r="E7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F7" t="str">
+        <v>+41 21 987 6543</v>
+      </c>
+      <c r="G7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H7" t="str">
+        <v>lausannephotoscan.ch</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Avenue de la Gare 15</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>Lausanne</v>
+      </c>
+      <c r="L7" t="str">
+        <v>1003</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Switzerland</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Prints, Slides 35mm</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>Super 8</v>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v>Mail, Digital download</v>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v>Expert en numérisation de photos et films argentiques. Service rapide et soigné pour tous vos projets de préservation.</v>
+      </c>
+      <c r="W7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X7" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>46.5197</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>6.6323</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>lausanne-photo-scan</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2025-10-16T08:13:28.921Z</v>
+      </c>
+      <c r="B8" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Brussels Heritage Digital</v>
+      </c>
+      <c r="D8" t="str">
+        <v>info@brusselsheritage.be</v>
+      </c>
+      <c r="E8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F8" t="str">
+        <v>+32 2 555 1234</v>
+      </c>
+      <c r="G8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H8" t="str">
+        <v>brusselsheritage.be</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Boulevard Anspach 50</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>Brussels</v>
+      </c>
+      <c r="L8" t="str">
+        <v>1000</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Belgium</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Prints, Albums, Negatives 35mm, Slides 35mm</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>8mm, Super 8, 16mm</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>VHS, VHS-C, MiniDV</v>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v>In-person, Mail, Digital download</v>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v>Centre de numérisation professionnel à Bruxelles. Plus de 20 ans d expertise dans la préservation de vos souvenirs familiaux.</v>
+      </c>
+      <c r="W8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>50.8503</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>4.3517</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>brussels-heritage-digital</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2025-10-16T08:13:33.037Z</v>
+      </c>
+      <c r="B9" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Antwerp Media Transfer</v>
+      </c>
+      <c r="D9" t="str">
+        <v>contact@antwerpmt.be</v>
+      </c>
+      <c r="E9" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="F9" t="str">
+        <v>+32 3 789 4561</v>
+      </c>
+      <c r="G9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H9" t="str">
+        <v>antwerpmt.be</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Meir 85</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>Antwerp</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2000</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Belgium</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Prints, Negatives 35mm</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>Super 8</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>VHS, Betamax, Digital8</v>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v>In-person, Mail</v>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v>Spécialiste de la conversion vidéo et photo à Anvers. Qualité professionnelle garantie pour tous vos médias anciens.</v>
+      </c>
+      <c r="W9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>51.2194</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>4.4025</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>antwerp-media-transfer</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2025-10-16T08:13:36.904Z</v>
+      </c>
+      <c r="B10" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Lyon Mémoire Numérique</v>
+      </c>
+      <c r="D10" t="str">
+        <v>contact@lyonmemoire.fr</v>
+      </c>
+      <c r="E10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F10" t="str">
+        <v>+33 4 78 56 34 12</v>
+      </c>
+      <c r="G10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H10" t="str">
+        <v>lyonmemoire.fr</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Place Bellecour 12</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>Lyon</v>
+      </c>
+      <c r="L10" t="str">
+        <v>69002</v>
+      </c>
+      <c r="M10" t="str">
+        <v>France</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Prints, Albums, Negatives 35mm, Slides 35mm</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>8mm, Super 8</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>VHS, MiniDV</v>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v>In-person, Mail, Digital download</v>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v>Votre expert en numérisation à Lyon. Service personnalisé et professionnel pour préserver vos précieux souvenirs de famille.</v>
+      </c>
+      <c r="W10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>45.7640</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>4.8357</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>lyon-memoire-numerique</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2025-10-16T08:13:41.049Z</v>
+      </c>
+      <c r="B11" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Marseille Photo Lab</v>
+      </c>
+      <c r="D11" t="str">
+        <v>info@marseillephotolab.fr</v>
+      </c>
+      <c r="E11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F11" t="str">
+        <v>+33 4 91 23 45 67</v>
+      </c>
+      <c r="G11" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="H11" t="str">
+        <v>marseillephotolab.fr</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Vieux-Port, Quai du Port 30</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>Marseille</v>
+      </c>
+      <c r="L11" t="str">
+        <v>13002</v>
+      </c>
+      <c r="M11" t="str">
+        <v>France</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Prints, Negatives 35mm, Slides 35mm</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v>Super 8, 16mm</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>VHS</v>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v>In-person, Digital download</v>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v>Laboratoire photo professionnel au cœur de Marseille. Numérisation haute résolution de vos photos, négatifs et films.</v>
+      </c>
+      <c r="W11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>43.2965</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>5.3698</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>marseille-photo-lab</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2025-10-16T08:13:44.824Z</v>
+      </c>
+      <c r="B12" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Nice Riviera Scan</v>
+      </c>
+      <c r="D12" t="str">
+        <v>contact@nicerivierascan.fr</v>
+      </c>
+      <c r="E12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F12" t="str">
+        <v>+33 4 93 87 65 43</v>
+      </c>
+      <c r="G12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H12" t="str">
+        <v>nicerivierascan.fr</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Promenade des Anglais 45</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Nice</v>
+      </c>
+      <c r="L12" t="str">
+        <v>06000</v>
+      </c>
+      <c r="M12" t="str">
+        <v>France</v>
+      </c>
+      <c r="N12" t="str">
+        <v>Prints, Albums</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v>8mm, Super 8</v>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v>VHS, MiniDV, Digital8</v>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v>Mail, Digital download</v>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v>Service de numérisation sur la Côte d Azur. Qualité premium pour vos films et photos de vacances et souvenirs familiaux.</v>
+      </c>
+      <c r="W12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X12" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>43.7102</v>
+      </c>
+      <c r="AB12" t="str">
+        <v>7.2620</v>
+      </c>
+      <c r="AC12" t="str">
+        <v>nice-riviera-scan</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2025-10-16T08:13:49.096Z</v>
+      </c>
+      <c r="B13" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Montréal Film &amp; Photo</v>
+      </c>
+      <c r="D13" t="str">
+        <v>info@montrealfilm.ca</v>
+      </c>
+      <c r="E13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F13" t="str">
+        <v>+1 514 555 1234</v>
+      </c>
+      <c r="G13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H13" t="str">
+        <v>montrealfilm.ca</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Rue Sainte-Catherine 1500</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>Montreal</v>
+      </c>
+      <c r="L13" t="str">
+        <v>H3G 1M8</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="N13" t="str">
+        <v>Prints, Albums, Negatives 35mm, Slides 35mm</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v>8mm, Super 8, 16mm</v>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v>VHS, VHS-C, Betamax, MiniDV</v>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v>In-person, Mail, Digital download</v>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v>Expert en numérisation à Montréal depuis 15 ans. Service bilingue pour vos photos, films et vidéos de famille.</v>
+      </c>
+      <c r="W13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>45.5017</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>-73.5673</v>
+      </c>
+      <c r="AC13" t="str">
+        <v>montreal-film-photo</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2025-10-16T08:13:53.460Z</v>
+      </c>
+      <c r="B14" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Toronto Memory Preservation</v>
+      </c>
+      <c r="D14" t="str">
+        <v>contact@torontomemory.ca</v>
+      </c>
+      <c r="E14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F14" t="str">
+        <v>+1 416 555 7890</v>
+      </c>
+      <c r="G14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H14" t="str">
+        <v>torontomemory.ca</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Yonge Street 789</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>Toronto</v>
+      </c>
+      <c r="L14" t="str">
+        <v>M5B 1Y8</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="N14" t="str">
+        <v>Prints, Negatives 35mm, Slides 35mm</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v>Super 8</v>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v>VHS, MiniDV, Digital8</v>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v>In-person, Mail, Digital download</v>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v>Professional digitization services in Toronto. We preserve your family memories with state-of-the-art technology and care.</v>
+      </c>
+      <c r="W14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X14" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>43.6532</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>-79.3832</v>
+      </c>
+      <c r="AC14" t="str">
+        <v>toronto-memory-preservation</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -598,22 +598,22 @@
         <v>12 65 25 15 45</v>
       </c>
       <c r="G3" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="H3" t="str">
         <v>test.com</v>
       </c>
       <c r="I3" t="str">
-        <v>68 Av. Jean Jaurès</v>
+        <v>39 Rue Bergeret</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Souillac</v>
+        <v>Bordeaux</v>
       </c>
       <c r="L3" t="str">
-        <v>46200</v>
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>France</v>
@@ -657,11 +657,11 @@
       <c r="Z3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="AA3" t="str">
-        <v>44.9046780724082</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>1.4671430115554622</v>
+      <c r="AA3">
+        <v>44.82961</v>
+      </c>
+      <c r="AB3">
+        <v>-0.56748</v>
       </c>
       <c r="AC3" t="str">
         <v>ngoc-test</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -658,10 +658,10 @@
         <v>TRUE</v>
       </c>
       <c r="AA3">
-        <v>44.82961</v>
+        <v>44.83179963473438</v>
       </c>
       <c r="AB3">
-        <v>-0.56748</v>
+        <v>-0.5680008374633064</v>
       </c>
       <c r="AC3" t="str">
         <v>ngoc-test</v>

--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1646,9 +1646,187 @@
         <v>toronto-memory-preservation</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2025-10-15T09:34:01.258Z</v>
+      </c>
+      <c r="B15" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Photolix</v>
+      </c>
+      <c r="D15" t="str">
+        <v>lyon@photolix.fr</v>
+      </c>
+      <c r="E15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F15" t="str">
+        <v>04 78 89 33 13</v>
+      </c>
+      <c r="G15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H15" t="str">
+        <v>www.photolix.fr</v>
+      </c>
+      <c r="I15" t="str">
+        <v>65 cours Vitton</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>Lyon</v>
+      </c>
+      <c r="L15" t="str">
+        <v>69006</v>
+      </c>
+      <c r="M15" t="str">
+        <v>France</v>
+      </c>
+      <c r="N15" t="str">
+        <v>"Negatives 35mm, Medium format 120/220, Polaroid/Instax, Prints, Slides 35mm, Large format"</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v>"8mm, 9.5mm Pathé, Super 8, 16mm"</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v>"VHS, Video8/Hi8, MiniDV, DVCAM, Digital8, VHS-C, Betamax, U-Matic"</v>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v>"USB, Download link, DVD/Blu-ray"</v>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2025-10-16T10:07:29.740Z</v>
+      </c>
+      <c r="B16" t="str">
+        <v>digitization</v>
+      </c>
+      <c r="C16" t="str">
+        <v>PANAJOU</v>
+      </c>
+      <c r="D16" t="str">
+        <v>contact@panajou.fr</v>
+      </c>
+      <c r="E16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F16" t="str">
+        <v>+33556442269</v>
+      </c>
+      <c r="G16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="H16" t="str">
+        <v>https://www.panajou.fr/</v>
+      </c>
+      <c r="I16" t="str">
+        <v>32 allées de Tourny</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>BORDEAUX</v>
+      </c>
+      <c r="L16" t="str">
+        <v>33000</v>
+      </c>
+      <c r="M16" t="str">
+        <v>France</v>
+      </c>
+      <c r="N16" t="str">
+        <v>"Prints, Albums, Negatives 35mm, Medium format 120/220, Slides 35mm, Large format, Polaroid/Instax"</v>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v>"8mm, 9.5mm Pathé, Super 8, 16mm"</v>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v>"VHS, Video8/Hi8, MiniDV, DVCAM, VHS-C, Digital8"</v>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v>USB</v>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="X16" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/partner-submissions.xlsx
+++ b/partner-submissions.xlsx
@@ -655,7 +655,7 @@
         <v>TRUE</v>
       </c>
       <c r="Z3" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AA3">
         <v>44.83179963473438</v>
